--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487694_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487694_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1609</v>
+        <v>5.297</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2087</v>
+        <v>4.2903</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9523</v>
+        <v>1.0068</v>
       </c>
       <c r="G2" t="n">
         <v>2.0856</v>
@@ -610,13 +610,13 @@
         <v>2.1344</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0004</v>
+        <v>0.1365</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1233</v>
+        <v>0.2049</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1229</v>
+        <v>-0.0684</v>
       </c>
       <c r="V2" t="n">
         <v>2.8809</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3616</v>
+        <v>3.3498</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9924</v>
+        <v>5.2532</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6308</v>
+        <v>-1.9034</v>
       </c>
       <c r="G3" t="n">
         <v>1.9711</v>
@@ -688,13 +688,13 @@
         <v>3.1045</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.7397</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1839</v>
+        <v>0.4447</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5676</v>
+        <v>0.295</v>
       </c>
       <c r="V3" t="n">
         <v>1.6092</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. APARICIO IZQUIERDO</t>
+          <t>A. JIMENEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7476</v>
+        <v>3.0123</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5598</v>
+        <v>1.6078</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1878</v>
+        <v>1.4045</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5016</v>
+        <v>2.6882</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5316</v>
+        <v>1.1394</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03</v>
+        <v>1.5488</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9939</v>
+        <v>1.771</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1164</v>
+        <v>0.3501</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8775</v>
+        <v>1.4209</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4923</v>
+        <v>0.9172</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4152</v>
+        <v>0.7893</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.9075</v>
+        <v>0.1279</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.194</v>
+        <v>0.9702</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1344</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9403</v>
+        <v>0.9702</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4428</v>
+        <v>-0.646</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1839</v>
+        <v>-0.1632</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2589</v>
+        <v>-0.4828</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9973</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5164</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4809</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. JIMENEZ FERNANDEZ</t>
+          <t>A. APARICIO IZQUIERDO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5608</v>
+        <v>2.9416</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3471</v>
+        <v>1.7811</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2137</v>
+        <v>1.1606</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6882</v>
+        <v>1.5016</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1394</v>
+        <v>1.5316</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5488</v>
+        <v>-0.03</v>
       </c>
       <c r="J5" t="n">
-        <v>1.771</v>
+        <v>2.9939</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3501</v>
+        <v>1.1164</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4209</v>
+        <v>1.8775</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9172</v>
+        <v>-1.4923</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7893</v>
+        <v>0.4152</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1279</v>
+        <v>-1.9075</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9702</v>
+        <v>-0.194</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.1344</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9702</v>
+        <v>1.9403</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0976</v>
+        <v>0.6368</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.424</v>
+        <v>0.4051</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6736</v>
+        <v>0.2316</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.9973</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.5164</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.4809</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4371</v>
+        <v>1.842</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9714</v>
+        <v>2.1311</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5344</v>
+        <v>-0.2891</v>
       </c>
       <c r="G6" t="n">
         <v>0.1839</v>
@@ -922,13 +922,13 @@
         <v>0.9702</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1471</v>
+        <v>0.5521</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5175</v>
+        <v>0.6771</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3703</v>
+        <v>-0.125</v>
       </c>
       <c r="V6" t="n">
         <v>0.3299</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6194</v>
+        <v>0.6582</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4108</v>
+        <v>0.8312</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2086</v>
+        <v>-0.173</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2364</v>
@@ -1000,13 +1000,13 @@
         <v>1.3582</v>
       </c>
       <c r="S7" t="n">
-        <v>1.6736</v>
+        <v>0.7125</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.3322</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7618</v>
+        <v>0.3802</v>
       </c>
       <c r="V7" t="n">
         <v>-1.1761</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8218</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6092</v>
+        <v>-0.1482</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2127</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>2.5768</v>
@@ -1078,13 +1078,13 @@
         <v>1.9403</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1384</v>
+        <v>0.2451</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3028</v>
+        <v>0.1581</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4413</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>-1.4027</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0655</v>
+        <v>-0.8931</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4554</v>
+        <v>-1.5555</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3898</v>
+        <v>0.6624</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7628</v>
@@ -1156,13 +1156,13 @@
         <v>0.9702</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1581</v>
+        <v>0.3306</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2434</v>
+        <v>0.1433</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0852</v>
+        <v>0.1873</v>
       </c>
       <c r="V9" t="n">
         <v>-0.4609</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1513</v>
+        <v>-0.9907</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2896</v>
+        <v>0.4502</v>
       </c>
       <c r="F10" t="n">
         <v>-1.4409</v>
@@ -1234,10 +1234,10 @@
         <v>0.5821</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3275</v>
+        <v>-0.1668</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3634</v>
+        <v>-0.2027</v>
       </c>
       <c r="U10" t="n">
         <v>0.0359</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.961</v>
+        <v>-1.0485</v>
       </c>
       <c r="E11" t="n">
-        <v>0.051</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.012</v>
+        <v>-1.8212</v>
       </c>
       <c r="G11" t="n">
         <v>0.6448</v>
@@ -1312,13 +1312,13 @@
         <v>1.7463</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.382</v>
+        <v>0.5305</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5451</v>
+        <v>0.1766</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1631</v>
+        <v>0.3539</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8358</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4504</v>
+        <v>-3.1078</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9966</v>
+        <v>-3.7358</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5462</v>
+        <v>0.628</v>
       </c>
       <c r="G12" t="n">
         <v>-4.6861</v>
@@ -1390,13 +1390,13 @@
         <v>0.7761</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2001</v>
+        <v>0.1424</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.424</v>
+        <v>-0.1632</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2239</v>
+        <v>0.3056</v>
       </c>
       <c r="V12" t="n">
         <v>0.6597</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.4374</v>
+        <v>10.3456</v>
       </c>
       <c r="E13" t="n">
-        <v>10.7696</v>
+        <v>11.6781</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3324</v>
+        <v>-1.3323</v>
       </c>
       <c r="G13" t="n">
         <v>5.784600000000001</v>
@@ -1468,13 +1468,13 @@
         <v>16.4928</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3047</v>
+        <v>3.2134</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1045</v>
+        <v>2.0129</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2005</v>
+        <v>1.2002</v>
       </c>
       <c r="V13" t="n">
         <v>0.3776000000000004</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.3377</v>
+        <v>5.5096</v>
       </c>
       <c r="E14" t="n">
-        <v>4.7872</v>
+        <v>3.9864</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5505</v>
+        <v>1.5232</v>
       </c>
       <c r="G14" t="n">
         <v>1.0712</v>
@@ -1546,13 +1546,13 @@
         <v>2.7164</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3647</v>
+        <v>0.5367</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2875</v>
+        <v>0.4867</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0772</v>
+        <v>0.0499</v>
       </c>
       <c r="V14" t="n">
         <v>3.1257</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1956</v>
+        <v>4.0053</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0869</v>
+        <v>4.7876</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8913</v>
+        <v>-0.7823</v>
       </c>
       <c r="G15" t="n">
         <v>2.8757</v>
@@ -1624,13 +1624,13 @@
         <v>1.3582</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3102</v>
+        <v>-0.5004999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9085</v>
+        <v>-0.2078</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4017</v>
+        <v>-0.2927</v>
       </c>
       <c r="V15" t="n">
         <v>1.2421</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.507</v>
+        <v>1.3251</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5946</v>
+        <v>1.4945</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0877</v>
+        <v>-0.1694</v>
       </c>
       <c r="G16" t="n">
         <v>2.4252</v>
@@ -1702,13 +1702,13 @@
         <v>2.3284</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0063</v>
+        <v>-0.1881</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1222</v>
+        <v>0.0221</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1285</v>
+        <v>-0.2103</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3299</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6504</v>
+        <v>0.5319</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2629</v>
+        <v>2.0627</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.6126</v>
+        <v>-1.5308</v>
       </c>
       <c r="G17" t="n">
         <v>-0.5101</v>
@@ -1780,13 +1780,13 @@
         <v>0.9702</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1395</v>
+        <v>-0.258</v>
       </c>
       <c r="T17" t="n">
-        <v>0.074</v>
+        <v>-0.1262</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2135</v>
+        <v>-0.1318</v>
       </c>
       <c r="V17" t="n">
         <v>0.3299</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9891</v>
+        <v>-1.453</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.174</v>
+        <v>-0.4743</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8151</v>
+        <v>-0.9787</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6461</v>
@@ -1858,13 +1858,13 @@
         <v>2.1344</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0552</v>
+        <v>0.5913</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5596</v>
+        <v>0.2593</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4955</v>
+        <v>0.332</v>
       </c>
       <c r="V18" t="n">
         <v>0.3481</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. MARINEZ FERNANDEZ-URRUTIA</t>
+          <t>P. ROSSI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7863</v>
+        <v>-1.7564</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7972</v>
+        <v>-1.0745</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9891</v>
+        <v>-0.6818</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7088</v>
+        <v>-2.4012</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-1.6304</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0467</v>
+        <v>-0.7708</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3843</v>
+        <v>-0.987</v>
       </c>
       <c r="K19" t="n">
-        <v>0.103</v>
+        <v>-1.0504</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2813</v>
+        <v>0.0634</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.0931</v>
+        <v>-1.4142</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8585</v>
+        <v>-0.58</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2346</v>
+        <v>-0.8342000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7761</v>
+        <v>0.194</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
         <v>1.1642</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0852</v>
+        <v>-0.773</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2412</v>
+        <v>-0.3413</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1559</v>
+        <v>-0.4318</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2161</v>
+        <v>1.2239</v>
       </c>
       <c r="W19" t="n">
+        <v>1.2239</v>
+      </c>
+      <c r="X19" t="n">
         <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>-0.2161</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. ROSSI</t>
+          <t>D. MARINEZ FERNANDEZ-URRUTIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8198</v>
+        <v>-2.1589</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9744</v>
+        <v>-0.8973</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8454</v>
+        <v>-1.2616</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.4012</v>
+        <v>-0.7088</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6304</v>
+        <v>-0.7554999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7708</v>
+        <v>0.0467</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.987</v>
+        <v>1.3843</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.0504</v>
+        <v>0.103</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0634</v>
+        <v>1.2813</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4142</v>
+        <v>-2.0931</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.58</v>
+        <v>-0.8585</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8342000000000001</v>
+        <v>-1.2346</v>
       </c>
       <c r="P20" t="n">
-        <v>0.194</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R20" t="n">
         <v>1.1642</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8365</v>
+        <v>-0.4579</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2412</v>
+        <v>-0.3413</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5953000000000001</v>
+        <v>-0.1166</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2239</v>
+        <v>-0.2161</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2161</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6113</v>
+        <v>-3.5474</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9795</v>
+        <v>-2.7793</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6318</v>
+        <v>-0.7681</v>
       </c>
       <c r="G21" t="n">
         <v>-0.1761</v>
@@ -2092,13 +2092,13 @@
         <v>1.3582</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.443</v>
+        <v>-0.3791</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5451</v>
+        <v>-0.3449</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1021</v>
+        <v>-0.0342</v>
       </c>
       <c r="V21" t="n">
         <v>-1.44</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.1612</v>
+        <v>-5.7975</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7585</v>
+        <v>-2.5583</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.4027</v>
+        <v>-3.2392</v>
       </c>
       <c r="G22" t="n">
         <v>-3.2248</v>
@@ -2170,13 +2170,13 @@
         <v>0.5821</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9946</v>
+        <v>-0.6309</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.3326</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4618</v>
+        <v>-0.2983</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5537</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.7602</v>
+        <v>-6.0961</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.7157</v>
+        <v>-3.2152</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.0445</v>
+        <v>-2.8809</v>
       </c>
       <c r="G23" t="n">
         <v>-4.4896</v>
@@ -2248,13 +2248,13 @@
         <v>1.7463</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9094</v>
+        <v>-0.2453</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.775</v>
+        <v>-0.2745</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1343</v>
+        <v>0.0292</v>
       </c>
       <c r="V23" t="n">
         <v>-3.1075</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.437200000000001</v>
+        <v>-9.4374</v>
       </c>
       <c r="E24" t="n">
         <v>1.3323</v>
       </c>
       <c r="F24" t="n">
-        <v>-10.7697</v>
+        <v>-10.7696</v>
       </c>
       <c r="G24" t="n">
         <v>-5.7846</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.6992</v>
+        <v>-3.699199999999999</v>
       </c>
       <c r="I24" t="n">
         <v>-2.0856</v>
@@ -2332,7 +2332,7 @@
         <v>-1.2005</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.1044</v>
+        <v>-1.1046</v>
       </c>
       <c r="V24" t="n">
         <v>-0.3775000000000004</v>
